--- a/artfynd/A 8654-2026 artfynd.xlsx
+++ b/artfynd/A 8654-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131830086</v>
       </c>
       <c r="B2" t="n">
-        <v>58274</v>
+        <v>58276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>131830517</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131830497</v>
       </c>
       <c r="B4" t="n">
-        <v>58059</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8654-2026 artfynd.xlsx
+++ b/artfynd/A 8654-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131830086</v>
       </c>
       <c r="B2" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131830497</v>
       </c>
       <c r="B4" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8654-2026 artfynd.xlsx
+++ b/artfynd/A 8654-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131830086</v>
+        <v>131830517</v>
       </c>
       <c r="B2" t="n">
-        <v>58322</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,16 +703,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570533</v>
+        <v>570405</v>
       </c>
       <c r="R2" t="n">
-        <v>6430476</v>
+        <v>6430596</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,27 +785,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131830517</v>
+        <v>131830086</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>58349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,12 +813,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570405</v>
+        <v>570533</v>
       </c>
       <c r="R3" t="n">
-        <v>6430596</v>
+        <v>6430476</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,11 +868,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
         <v>131830497</v>
       </c>
       <c r="B4" t="n">
-        <v>58107</v>
+        <v>58134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
